--- a/india_compliance/gst_india/data/test_gstr2a_export_golden.xlsx
+++ b/india_compliance/gst_india/data/test_gstr2a_export_golden.xlsx
@@ -6393,7 +6393,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GSTN</t>
+          <t>LEGAL NAME</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
